--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ29"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,47 +1108,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67768808</v>
+        <v>136390002</v>
       </c>
       <c r="B6" t="n">
-        <v>93235</v>
+        <v>92496</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4789</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svavelticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Laetiporus sulphureus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Bull.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Turebacken, Boh</t>
+          <t>Turebacksvägen, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>317440</v>
+        <v>317404</v>
       </c>
       <c r="R6" t="n">
-        <v>6458312</v>
+        <v>6458210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,12 +1180,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-10-01</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-10-01</t>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,60 +1211,59 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Via Ellen Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67768808</t>
+          <t>https://artportalen.se/Sighting/136390002</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111440205</v>
+        <v>67768808</v>
       </c>
       <c r="B7" t="n">
-        <v>92567</v>
+        <v>93235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Turebacksvägen, Boh</t>
+          <t>Turebacken, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>317351</v>
+        <v>317440</v>
       </c>
       <c r="R7" t="n">
-        <v>6458174</v>
+        <v>6458312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,12 +1290,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2017-10-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2017-10-01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,63 +1322,57 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111440205</t>
+          <t>https://artportalen.se/Sighting/67768808</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>102199609</v>
+        <v>111440205</v>
       </c>
       <c r="B8" t="n">
-        <v>56888</v>
+        <v>92567</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100041</v>
+        <v>6031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hasselsnok</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coronella austriaca</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Laurenti, 1768</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grinddalen 14, Boh</t>
+          <t>Turebacksvägen, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>317412</v>
+        <v>317351</v>
       </c>
       <c r="R8" t="n">
-        <v>6458091</v>
+        <v>6458174</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1393,17 +1396,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Skadad men levande, eventuellt skadad av kråka eller skata</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,38 +1428,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102199609</t>
+          <t>https://artportalen.se/Sighting/111440205</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104015491</v>
+        <v>102199609</v>
       </c>
       <c r="B9" t="n">
-        <v>57950</v>
+        <v>56888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100041</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Laurenti, 1768</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1469,27 +1467,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grinddalen, skogen, Boh</t>
+          <t>Grinddalen 14, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>317405</v>
+        <v>317412</v>
       </c>
       <c r="R9" t="n">
-        <v>6458115</v>
+        <v>6458091</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1513,12 +1508,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
+          <t>2022-06-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
+          <t>2022-06-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Skadad men levande, eventuellt skadad av kråka eller skata</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1527,33 +1527,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Björn Larsson, Moa Pettersson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104015491</t>
+          <t>https://artportalen.se/Sighting/102199609</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132783038</v>
+        <v>104015491</v>
       </c>
       <c r="B10" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,23 +1588,23 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grinddalen, Boh</t>
+          <t>Grinddalen, skogen, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>317392</v>
+        <v>317405</v>
       </c>
       <c r="R10" t="n">
-        <v>6458107</v>
+        <v>6458115</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1627,12 +1628,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,24 +1648,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Via Ellen Larsson</t>
+          <t>Björn Larsson, Moa Pettersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132783038</t>
+          <t>https://artportalen.se/Sighting/104015491</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133970214</v>
+        <v>132783038</v>
       </c>
       <c r="B11" t="n">
         <v>57972</v>
@@ -1707,17 +1708,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grinddalen källpåverkad blandskog, Boh</t>
+          <t>Grinddalen, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>317401</v>
+        <v>317392</v>
       </c>
       <c r="R11" t="n">
-        <v>6458102</v>
+        <v>6458107</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,22 +1742,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>19:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>19:30</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1776,22 +1767,22 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Via Ellen Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133970214</t>
+          <t>https://artportalen.se/Sighting/132783038</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133283114</v>
+        <v>133970214</v>
       </c>
       <c r="B12" t="n">
-        <v>56915</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,16 +1790,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1821,7 +1812,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
@@ -1832,17 +1822,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grinddalen dammen, Boh</t>
+          <t>Grinddalen källpåverkad blandskog, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>317394</v>
+        <v>317401</v>
       </c>
       <c r="R12" t="n">
-        <v>6458070</v>
+        <v>6458102</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1866,17 +1856,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Snoken hade fångat en vanlig groda som tog lite tid att svälja</t>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,14 +1880,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal bevattningsdamm, nästa igenvuxen</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1902,22 +1891,22 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Ellen Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133283114</t>
+          <t>https://artportalen.se/Sighting/133970214</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129729452</v>
+        <v>133283114</v>
       </c>
       <c r="B13" t="n">
-        <v>57947</v>
+        <v>56915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1925,21 +1914,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102977</v>
+        <v>100088</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1947,6 +1936,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
@@ -1957,17 +1947,17 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grinddalen, skogen, Boh</t>
+          <t>Grinddalen dammen, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>317405</v>
+        <v>317394</v>
       </c>
       <c r="R13" t="n">
-        <v>6458115</v>
+        <v>6458070</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1991,12 +1981,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Snoken hade fångat en vanlig groda som tog lite tid att svälja</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,55 +2000,61 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal bevattningsdamm, nästa igenvuxen</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Björn Larsson, Ellen Larsson</t>
+          <t>Via Ellen Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129729452</t>
+          <t>https://artportalen.se/Sighting/133283114</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123245162</v>
+        <v>129729452</v>
       </c>
       <c r="B14" t="n">
-        <v>58388</v>
+        <v>57947</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>102977</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2105,22 +2106,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2140,44 +2131,44 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Björn Larsson, Ellen Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123245162</t>
+          <t>https://artportalen.se/Sighting/129729452</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123245085</v>
+        <v>123245162</v>
       </c>
       <c r="B15" t="n">
-        <v>58327</v>
+        <v>58388</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>103001</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2189,7 +2180,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2270,16 +2261,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123245085</t>
+          <t>https://artportalen.se/Sighting/123245162</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>71343303</v>
+        <v>123245085</v>
       </c>
       <c r="B16" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2287,48 +2278,49 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grinddalen, Boh</t>
+          <t>Grinddalen, skogen, Boh</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>317392</v>
+        <v>317405</v>
       </c>
       <c r="R16" t="n">
-        <v>6458107</v>
+        <v>6458115</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2352,17 +2344,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-05-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>två par, två holkar</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,27 +2374,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71343303</t>
+          <t>https://artportalen.se/Sighting/123245085</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123245155</v>
+        <v>71343303</v>
       </c>
       <c r="B17" t="n">
-        <v>58636</v>
+        <v>58439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2405,49 +2402,48 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103044</v>
+        <v>103018</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grinddalen, skogen, Boh</t>
+          <t>Grinddalen, Boh</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>317405</v>
+        <v>317392</v>
       </c>
       <c r="R17" t="n">
-        <v>6458115</v>
+        <v>6458107</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2471,22 +2467,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2018-05-15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2018-05-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>två par, två holkar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,27 +2492,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123245155</t>
+          <t>https://artportalen.se/Sighting/71343303</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133282638</v>
+        <v>123245155</v>
       </c>
       <c r="B18" t="n">
-        <v>30293</v>
+        <v>58636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2529,42 +2520,49 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>200985</v>
+        <v>103044</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Turebacksvägen, Boh</t>
+          <t>Grinddalen, skogen, Boh</t>
         </is>
       </c>
       <c r="Q18" t="n">
         <v>317405</v>
       </c>
       <c r="R18" t="n">
-        <v>6458184</v>
+        <v>6458115</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2588,17 +2586,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre barrskog med hassel</t>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2607,34 +2610,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133282638</t>
+          <t>https://artportalen.se/Sighting/123245155</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>108776338</v>
+        <v>133282638</v>
       </c>
       <c r="B19" t="n">
-        <v>58085</v>
+        <v>30293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2642,41 +2644,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205976</v>
+        <v>200985</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grinddalen, Boh</t>
+          <t>Turebacksvägen, Boh</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>317411</v>
+        <v>317405</v>
       </c>
       <c r="R19" t="n">
-        <v>6458143</v>
+        <v>6458184</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2700,12 +2703,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre barrskog med hassel</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2714,6 +2722,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2725,22 +2734,22 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Via Ellen Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108776338</t>
+          <t>https://artportalen.se/Sighting/133282638</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>71343353</v>
+        <v>108776338</v>
       </c>
       <c r="B20" t="n">
-        <v>58790</v>
+        <v>58085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2748,25 +2757,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208245</v>
+        <v>205976</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2777,13 +2785,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>317392</v>
+        <v>317411</v>
       </c>
       <c r="R20" t="n">
-        <v>6458107</v>
+        <v>6458143</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2807,12 +2815,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2018-05-11</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2018-05-11</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2838,16 +2846,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71343353</t>
+          <t>https://artportalen.se/Sighting/108776338</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>70603491</v>
+        <v>71343353</v>
       </c>
       <c r="B21" t="n">
-        <v>58817</v>
+        <v>58790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2855,50 +2863,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äggläggande</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>dammen, Boh</t>
+          <t>Grinddalen, Boh</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>317384</v>
+        <v>317392</v>
       </c>
       <c r="R21" t="n">
-        <v>6458066</v>
+        <v>6458107</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2922,12 +2922,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
+          <t>2018-05-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2018-04-14</t>
+          <t>2018-05-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,19 +2947,19 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ellen Larsson, Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70603491</t>
+          <t>https://artportalen.se/Sighting/71343353</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>71343372</v>
+        <v>70603491</v>
       </c>
       <c r="B22" t="n">
         <v>58817</v>
@@ -2993,31 +2993,27 @@
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>äggläggande</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grinddalen, Boh</t>
+          <t>dammen, Boh</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>317392</v>
+        <v>317384</v>
       </c>
       <c r="R22" t="n">
-        <v>6458107</v>
+        <v>6458066</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3041,12 +3037,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2018-05-11</t>
+          <t>2018-04-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2018-05-11</t>
+          <t>2018-04-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3066,19 +3062,19 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Ellen Larsson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71343372</t>
+          <t>https://artportalen.se/Sighting/70603491</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107930276</v>
+        <v>71343372</v>
       </c>
       <c r="B23" t="n">
         <v>58817</v>
@@ -3108,14 +3104,10 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>adult</t>
@@ -3124,27 +3116,23 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Grinddalen, Boh</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>317394</v>
+        <v>317392</v>
       </c>
       <c r="R23" t="n">
-        <v>6458055</v>
+        <v>6458107</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3168,12 +3156,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2018-05-11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2018-05-11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3182,31 +3170,30 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Moa Pettersson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Moa Pettersson, Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107930276</t>
+          <t>https://artportalen.se/Sighting/71343372</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>108776379</v>
+        <v>107930276</v>
       </c>
       <c r="B24" t="n">
         <v>58817</v>
@@ -3234,25 +3221,45 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grinddalen 14, Boh</t>
+          <t>Grinddalen, Boh</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>317412</v>
+        <v>317394</v>
       </c>
       <c r="R24" t="n">
-        <v>6458091</v>
+        <v>6458055</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3276,12 +3283,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-05-05</t>
+          <t>2023-04-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3297,27 +3304,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Moa Pettersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Moa Pettersson, Björn Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108776379</t>
+          <t>https://artportalen.se/Sighting/107930276</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132240800</v>
+        <v>108776379</v>
       </c>
       <c r="B25" t="n">
-        <v>58839</v>
+        <v>58817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3342,41 +3349,25 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grinddalen, dammen, Boh</t>
+          <t>Grinddalen 14, Boh</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>317387</v>
+        <v>317412</v>
       </c>
       <c r="R25" t="n">
-        <v>6458063</v>
+        <v>6458091</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3400,12 +3391,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2023-05-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3421,27 +3412,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Björn Larsson, Moa Pettersson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132240800</t>
+          <t>https://artportalen.se/Sighting/108776379</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>71844315</v>
+        <v>132240800</v>
       </c>
       <c r="B26" t="n">
-        <v>98194</v>
+        <v>58839</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3449,21 +3440,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220686</v>
+        <v>208249</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3471,22 +3462,36 @@
           <t>12</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grinddalen källpåverkad blandskog, Boh</t>
+          <t>Grinddalen, dammen, Boh</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>317401</v>
+        <v>317387</v>
       </c>
       <c r="R26" t="n">
-        <v>6458102</v>
+        <v>6458063</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3510,17 +3515,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>källpåverkad barrskog</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,30 +3529,31 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson, Moa Pettersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71844315</t>
+          <t>https://artportalen.se/Sighting/132240800</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>91604898</v>
+        <v>71844315</v>
       </c>
       <c r="B27" t="n">
         <v>98194</v>
@@ -3582,34 +3583,25 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grinddalen, skogen, Boh</t>
+          <t>Grinddalen källpåverkad blandskog, Boh</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>317405</v>
+        <v>317401</v>
       </c>
       <c r="R27" t="n">
-        <v>6458115</v>
+        <v>6458102</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3633,12 +3625,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2018-06-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-03-12</t>
+          <t>2018-06-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>källpåverkad barrskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3647,84 +3644,87 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Källpåverkad barrskog</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Björn Larsson</t>
+          <t>Ellen Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91604898</t>
+          <t>https://artportalen.se/Sighting/71844315</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>79043750</v>
+        <v>91604898</v>
       </c>
       <c r="B28" t="n">
-        <v>91060</v>
+        <v>98194</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>245628</v>
+        <v>220686</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granbronssopp</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Butyriboletus subappendiculatus</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dermek, Lazebn. &amp; J.Veselský) D.Arora &amp; J.L.Frank</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ulvesund grusgropen, Boh</t>
+          <t>Grinddalen, skogen, Boh</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>317422</v>
+        <v>317405</v>
       </c>
       <c r="R28" t="n">
-        <v>6458267</v>
+        <v>6458115</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3748,12 +3748,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2019-07-22</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2019-07-22</t>
+          <t>2021-03-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3766,63 +3766,80 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Källpåverkad barrskog</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ellen Larsson</t>
+          <t>Björn Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79043750</t>
+          <t>https://artportalen.se/Sighting/91604898</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>91518474</v>
+        <v>79043750</v>
       </c>
       <c r="B29" t="n">
-        <v>78261</v>
+        <v>91060</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6051522</v>
+        <v>245628</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Granbronssopp</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Elaphomyces nemoreus</t>
+          <t>Butyriboletus subappendiculatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Jeppson &amp; al.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Dermek, Lazebn. &amp; J.Veselský) D.Arora &amp; J.L.Frank</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekenhof, Boh</t>
+          <t>Ulvesund grusgropen, Boh</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>317430</v>
+        <v>317422</v>
       </c>
       <c r="R29" t="n">
-        <v>6458088</v>
+        <v>6458267</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3846,12 +3863,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2020-11-14</t>
+          <t>2019-07-22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2020-11-14</t>
+          <t>2019-07-22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3860,23 +3877,9 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>Lövskog</t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr">
-        <is>
-          <t>Göteborg-Herbarium GB</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>EL168-20</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3889,12 +3892,124 @@
           <t>Ellen Larsson</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79043750</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>91518474</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78261</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6051522</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Elaphomyces nemoreus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Jeppson &amp; al.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ekenhof, Boh</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>317430</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6458088</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2020-11-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2020-11-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>Göteborg-Herbarium GB</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>EL168-20</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ellen Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ellen Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
         <is>
           <t>Svenska tryffelprojektet</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91518474</t>
         </is>
@@ -3930,6 +4045,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136390002</v>
       </c>
       <c r="B6" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136390002</v>
       </c>
       <c r="B6" t="n">
-        <v>92497</v>
+        <v>92510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 35895-2026 artfynd.xlsx
+++ b/artfynd/A 35895-2026 artfynd.xlsx
@@ -1111,7 +1111,7 @@
         <v>136390002</v>
       </c>
       <c r="B6" t="n">
-        <v>92510</v>
+        <v>92511</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
